--- a/test-data/test3-clean.xlsx
+++ b/test-data/test3-clean.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,26 +434,26 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>FECHA DE ENTRADA</v>
+        <v>FECHA DE CONTRATO</v>
       </c>
       <c r="B7" t="str">
-        <v>20/06/2024</v>
+        <v>05/06/2024</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>FECHA DE SALIDA</v>
+        <v>FECHA DE ENTRADA</v>
       </c>
       <c r="B8" t="str">
-        <v>27/06/2024</v>
+        <v>20/06/2024</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HORA</v>
+        <v>FECHA DE SALIDA</v>
       </c>
       <c r="B9" t="str">
-        <v>15:00</v>
+        <v>27/06/2024</v>
       </c>
     </row>
     <row r="10">
@@ -461,131 +461,92 @@
         <v>HORA</v>
       </c>
       <c r="B10" t="str">
-        <v>11:00</v>
+        <v>15:00</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>NUMERO DE PERSONAS</v>
+        <v>HORA</v>
       </c>
       <c r="B11" t="str">
-        <v>10</v>
+        <v>11:00</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>TIPO DE PAGO</v>
+        <v>NUMERO DE PERSONAS</v>
       </c>
       <c r="B12" t="str">
-        <v>TARJETA</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Nombre</v>
+        <v>TIPO DE PAGO</v>
       </c>
       <c r="B13" t="str">
-        <v>1. Apellido</v>
-      </c>
-      <c r="C13" t="str">
-        <v>2. Apellido</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Fecha de nacimiento</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Nationality</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Tipo de documento de identidad</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Número de documento</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Soporte de documento</v>
-      </c>
-      <c r="I13" t="str">
-        <v>Dirección de residencia</v>
-      </c>
-      <c r="J13" t="str">
-        <v>Código municipio</v>
-      </c>
-      <c r="K13" t="str">
-        <v>Correo electrónico</v>
-      </c>
-      <c r="L13" t="str">
-        <v>Número de teléfono</v>
-      </c>
-      <c r="M13" t="str">
-        <v>Fecha de llegada</v>
-      </c>
-      <c r="N13" t="str">
-        <v>Fecha de salida</v>
-      </c>
-      <c r="O13" t="str">
-        <v>Parentesco</v>
+        <v>TARJETA</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Carlos</v>
+        <v>Nombre</v>
       </c>
       <c r="B14" t="str">
-        <v>López</v>
+        <v>1. Apellido</v>
       </c>
       <c r="C14" t="str">
-        <v>Fernández</v>
+        <v>2. Apellido</v>
       </c>
       <c r="D14" t="str">
-        <v>10/04/1980</v>
+        <v>Fecha de nacimiento</v>
       </c>
       <c r="E14" t="str">
-        <v>ESP</v>
+        <v>Nationality</v>
       </c>
       <c r="F14" t="str">
-        <v>NIF</v>
+        <v>Tipo de documento de identidad</v>
       </c>
       <c r="G14" t="str">
-        <v>56789012B</v>
+        <v>Número de documento</v>
       </c>
       <c r="H14" t="str">
-        <v>EEE555555</v>
+        <v>Soporte de documento</v>
       </c>
       <c r="I14" t="str">
-        <v>Calle Mayor 1, 46812 Riola, Valencia</v>
+        <v>Dirección de residencia</v>
       </c>
       <c r="J14" t="str">
-        <v>46215</v>
+        <v>Código municipio</v>
       </c>
       <c r="K14" t="str">
-        <v>carlos@example.com</v>
+        <v>Correo electrónico</v>
       </c>
       <c r="L14" t="str">
-        <v>+34633111222</v>
+        <v>Número de teléfono</v>
       </c>
       <c r="M14" t="str">
-        <v>20/06/2024</v>
+        <v>Fecha de llegada</v>
       </c>
       <c r="N14" t="str">
-        <v>27/06/2024</v>
+        <v>Fecha de salida</v>
       </c>
       <c r="O14" t="str">
-        <v>TI</v>
+        <v>Parentesco</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Laura</v>
+        <v>Carlos</v>
       </c>
       <c r="B15" t="str">
-        <v>Pérez</v>
+        <v>López</v>
       </c>
       <c r="C15" t="str">
-        <v>Gómez</v>
+        <v>Fernández</v>
       </c>
       <c r="D15" t="str">
-        <v>22/08/1982</v>
+        <v>10/04/1980</v>
       </c>
       <c r="E15" t="str">
         <v>ESP</v>
@@ -594,10 +555,10 @@
         <v>NIF</v>
       </c>
       <c r="G15" t="str">
-        <v>87654321X</v>
+        <v>56789012B</v>
       </c>
       <c r="H15" t="str">
-        <v>FFF666666</v>
+        <v>EEE555555</v>
       </c>
       <c r="I15" t="str">
         <v>Calle Mayor 1, 46812 Riola, Valencia</v>
@@ -606,10 +567,10 @@
         <v>46215</v>
       </c>
       <c r="K15" t="str">
-        <v>laura@example.com</v>
+        <v>carlos@example.com</v>
       </c>
       <c r="L15" t="str">
-        <v>+34644222333</v>
+        <v>+34633111222</v>
       </c>
       <c r="M15" t="str">
         <v>20/06/2024</v>
@@ -618,21 +579,21 @@
         <v>27/06/2024</v>
       </c>
       <c r="O15" t="str">
-        <v>CO</v>
+        <v>TI</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Diego</v>
+        <v>Laura</v>
       </c>
       <c r="B16" t="str">
-        <v>López</v>
+        <v>Pérez</v>
       </c>
       <c r="C16" t="str">
-        <v>Pérez</v>
+        <v>Gómez</v>
       </c>
       <c r="D16" t="str">
-        <v>15/03/2015</v>
+        <v>22/08/1982</v>
       </c>
       <c r="E16" t="str">
         <v>ESP</v>
@@ -641,10 +602,10 @@
         <v>NIF</v>
       </c>
       <c r="G16" t="str">
-        <v>23456789D</v>
+        <v>87654321X</v>
       </c>
       <c r="H16" t="str">
-        <v>GGG777777</v>
+        <v>FFF666666</v>
       </c>
       <c r="I16" t="str">
         <v>Calle Mayor 1, 46812 Riola, Valencia</v>
@@ -653,10 +614,10 @@
         <v>46215</v>
       </c>
       <c r="K16" t="str">
-        <v>carlos@example.com</v>
+        <v>laura@example.com</v>
       </c>
       <c r="L16" t="str">
-        <v>+34633111222</v>
+        <v>+34644222333</v>
       </c>
       <c r="M16" t="str">
         <v>20/06/2024</v>
@@ -665,45 +626,45 @@
         <v>27/06/2024</v>
       </c>
       <c r="O16" t="str">
-        <v>HJ</v>
+        <v>CO</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Amelie</v>
+        <v>Diego</v>
       </c>
       <c r="B17" t="str">
-        <v>Bernard</v>
+        <v>López</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>Pérez</v>
       </c>
       <c r="D17" t="str">
-        <v>07/02/1990</v>
+        <v>15/03/2015</v>
       </c>
       <c r="E17" t="str">
-        <v>FRA</v>
+        <v>ESP</v>
       </c>
       <c r="F17" t="str">
-        <v>PAS</v>
+        <v>NIF</v>
       </c>
       <c r="G17" t="str">
-        <v>13FT01234</v>
+        <v>23456789D</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>GGG777777</v>
       </c>
       <c r="I17" t="str">
-        <v>15 Cours Belsunce, Marseille, 13001</v>
+        <v>Calle Mayor 1, 46812 Riola, Valencia</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>46215</v>
       </c>
       <c r="K17" t="str">
-        <v>amelie@example.com</v>
+        <v>carlos@example.com</v>
       </c>
       <c r="L17" t="str">
-        <v>+33644556677</v>
+        <v>+34633111222</v>
       </c>
       <c r="M17" t="str">
         <v>20/06/2024</v>
@@ -712,45 +673,45 @@
         <v>27/06/2024</v>
       </c>
       <c r="O17" t="str">
-        <v>OT</v>
+        <v>HJ</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Andrei</v>
+        <v>Amelie</v>
       </c>
       <c r="B18" t="str">
-        <v>Popescu</v>
+        <v>Bernard</v>
       </c>
       <c r="C18" t="str">
-        <v>Ion</v>
+        <v/>
       </c>
       <c r="D18" t="str">
-        <v>14/11/1988</v>
+        <v>07/02/1990</v>
       </c>
       <c r="E18" t="str">
-        <v>ROU</v>
+        <v>FRA</v>
       </c>
       <c r="F18" t="str">
         <v>PAS</v>
       </c>
       <c r="G18" t="str">
-        <v>RO1234567</v>
+        <v>13FT01234</v>
       </c>
       <c r="H18" t="str">
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>Strada Victoriei 20, Bucuresti, 010091</v>
+        <v>15 Cours Belsunce, Marseille, 13001</v>
       </c>
       <c r="J18" t="str">
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>andrei@example.com</v>
+        <v>amelie@example.com</v>
       </c>
       <c r="L18" t="str">
-        <v>+40722123456</v>
+        <v>+33644556677</v>
       </c>
       <c r="M18" t="str">
         <v>20/06/2024</v>
@@ -764,40 +725,40 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>John</v>
+        <v>Andrei</v>
       </c>
       <c r="B19" t="str">
-        <v>Smith</v>
+        <v>Popescu</v>
       </c>
       <c r="C19" t="str">
-        <v>William</v>
+        <v>Ion</v>
       </c>
       <c r="D19" t="str">
-        <v>30/06/1975</v>
+        <v>14/11/1988</v>
       </c>
       <c r="E19" t="str">
-        <v>USA</v>
+        <v>ROU</v>
       </c>
       <c r="F19" t="str">
         <v>PAS</v>
       </c>
       <c r="G19" t="str">
-        <v>A12345678</v>
+        <v>RO1234567</v>
       </c>
       <c r="H19" t="str">
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>123 Main Street, New York, NY 10001</v>
+        <v>Strada Victoriei 20, Bucuresti, 010091</v>
       </c>
       <c r="J19" t="str">
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>jsmith@example.com</v>
+        <v>andrei@example.com</v>
       </c>
       <c r="L19" t="str">
-        <v>+12125551234</v>
+        <v>+40722123456</v>
       </c>
       <c r="M19" t="str">
         <v>20/06/2024</v>
@@ -811,40 +772,40 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Emma</v>
+        <v>John</v>
       </c>
       <c r="B20" t="str">
-        <v>Wilson</v>
+        <v>Smith</v>
       </c>
       <c r="C20" t="str">
-        <v>Brown</v>
+        <v>William</v>
       </c>
       <c r="D20" t="str">
-        <v>19/04/1994</v>
+        <v>30/06/1975</v>
       </c>
       <c r="E20" t="str">
-        <v>GBR</v>
+        <v>USA</v>
       </c>
       <c r="F20" t="str">
         <v>PAS</v>
       </c>
       <c r="G20" t="str">
-        <v>987654321</v>
+        <v>A12345678</v>
       </c>
       <c r="H20" t="str">
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>15 Baker Street, London, W1U 8EQ</v>
+        <v>123 Main Street, New York, NY 10001</v>
       </c>
       <c r="J20" t="str">
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>emma@example.com</v>
+        <v>jsmith@example.com</v>
       </c>
       <c r="L20" t="str">
-        <v>+447911123456</v>
+        <v>+12125551234</v>
       </c>
       <c r="M20" t="str">
         <v>20/06/2024</v>
@@ -858,40 +819,40 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Yuki</v>
+        <v>Emma</v>
       </c>
       <c r="B21" t="str">
-        <v>Tanaka</v>
+        <v>Wilson</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>Brown</v>
       </c>
       <c r="D21" t="str">
-        <v>03/01/1986</v>
+        <v>19/04/1994</v>
       </c>
       <c r="E21" t="str">
-        <v>JPN</v>
+        <v>GBR</v>
       </c>
       <c r="F21" t="str">
         <v>PAS</v>
       </c>
       <c r="G21" t="str">
-        <v>TK1234567</v>
+        <v>987654321</v>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>1-1 Shinjuku, Tokyo, 160-0022</v>
+        <v>15 Baker Street, London, W1U 8EQ</v>
       </c>
       <c r="J21" t="str">
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>yuki@example.com</v>
+        <v>emma@example.com</v>
       </c>
       <c r="L21" t="str">
-        <v>+81901234567</v>
+        <v>+447911123456</v>
       </c>
       <c r="M21" t="str">
         <v>20/06/2024</v>
@@ -905,40 +866,40 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Mohammed</v>
+        <v>Yuki</v>
       </c>
       <c r="B22" t="str">
-        <v>Alaoui</v>
+        <v>Tanaka</v>
       </c>
       <c r="C22" t="str">
-        <v>Benkiran</v>
+        <v/>
       </c>
       <c r="D22" t="str">
-        <v>25/09/1979</v>
+        <v>03/01/1986</v>
       </c>
       <c r="E22" t="str">
-        <v>MAR</v>
+        <v>JPN</v>
       </c>
       <c r="F22" t="str">
         <v>PAS</v>
       </c>
       <c r="G22" t="str">
-        <v>MA1234567</v>
+        <v>TK1234567</v>
       </c>
       <c r="H22" t="str">
         <v/>
       </c>
       <c r="I22" t="str">
-        <v>Rue Mohammed V 7, Casablanca, 20000</v>
+        <v>1-1 Shinjuku, Tokyo, 160-0022</v>
       </c>
       <c r="J22" t="str">
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>malaoui@example.com</v>
+        <v>yuki@example.com</v>
       </c>
       <c r="L22" t="str">
-        <v>+212661234567</v>
+        <v>+81901234567</v>
       </c>
       <c r="M22" t="str">
         <v>20/06/2024</v>
@@ -952,40 +913,40 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Wei</v>
+        <v>Mohammed</v>
       </c>
       <c r="B23" t="str">
-        <v>Zhang</v>
+        <v>Alaoui</v>
       </c>
       <c r="C23" t="str">
-        <v/>
+        <v>Benkiran</v>
       </c>
       <c r="D23" t="str">
-        <v>08/06/2000</v>
+        <v>25/09/1979</v>
       </c>
       <c r="E23" t="str">
-        <v>CHN</v>
+        <v>MAR</v>
       </c>
       <c r="F23" t="str">
-        <v>OTRO</v>
+        <v>PAS</v>
       </c>
       <c r="G23" t="str">
-        <v>CHN12345</v>
+        <v>MA1234567</v>
       </c>
       <c r="H23" t="str">
         <v/>
       </c>
       <c r="I23" t="str">
-        <v>Wangfujing Street 1, Beijing, 100010</v>
+        <v>Rue Mohammed V 7, Casablanca, 20000</v>
       </c>
       <c r="J23" t="str">
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>wzhang@example.com</v>
+        <v>malaoui@example.com</v>
       </c>
       <c r="L23" t="str">
-        <v>+8613912345678</v>
+        <v>+212661234567</v>
       </c>
       <c r="M23" t="str">
         <v>20/06/2024</v>
@@ -997,9 +958,56 @@
         <v>OT</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Wei</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Zhang</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>08/06/2000</v>
+      </c>
+      <c r="E24" t="str">
+        <v>CHN</v>
+      </c>
+      <c r="F24" t="str">
+        <v>OTRO</v>
+      </c>
+      <c r="G24" t="str">
+        <v>CHN12345</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>Wangfujing Street 1, Beijing, 100010</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v>wzhang@example.com</v>
+      </c>
+      <c r="L24" t="str">
+        <v>+8613912345678</v>
+      </c>
+      <c r="M24" t="str">
+        <v>20/06/2024</v>
+      </c>
+      <c r="N24" t="str">
+        <v>27/06/2024</v>
+      </c>
+      <c r="O24" t="str">
+        <v>OT</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O24"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/test-data/test3-clean.xlsx
+++ b/test-data/test3-clean.xlsx
@@ -121,10 +121,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -156,10 +156,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -401,7 +401,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>CODIGO 12345</v>
+        <v>CODIGO 0000004630</v>
       </c>
     </row>
     <row r="2">
